--- a/Events/Events.xlsx
+++ b/Events/Events.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daicampian\Desktop\TimeTool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daicampian\Desktop\TimeTool\Events\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A477B3C-3220-4028-B8DE-1C854D07E675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D3A294-A411-4350-87C8-6B9C68DE9C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -557,7 +557,7 @@
         <v>46142</v>
       </c>
       <c r="D4" s="2">
-        <v>0.77083333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="E4">
         <v>60</v>
@@ -591,7 +591,7 @@
         <v>46143</v>
       </c>
       <c r="D6" s="2">
-        <v>0.43055555555555558</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="E6">
         <v>45</v>

--- a/Events/Events.xlsx
+++ b/Events/Events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daicampian\Desktop\TimeTool\Events\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D3A294-A411-4350-87C8-6B9C68DE9C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656193D3-CBD3-4AA0-A6CB-77B66C063C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -591,7 +591,7 @@
         <v>46143</v>
       </c>
       <c r="D6" s="2">
-        <v>0.47222222222222221</v>
+        <v>0.43055555555555558</v>
       </c>
       <c r="E6">
         <v>45</v>
